--- a/data/trans_dic/P16A15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,64</t>
+          <t>2,05; 6,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,52</t>
+          <t>5,8; 13,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,4</t>
+          <t>4,36; 10,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 16,46</t>
+          <t>9,19; 16,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,43</t>
+          <t>5,01; 11,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 14,08</t>
+          <t>6,51; 14,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,58</t>
+          <t>6,49; 13,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,01</t>
+          <t>10,35; 16,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,17</t>
+          <t>4,04; 8,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 12,71</t>
+          <t>7,14; 12,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,9</t>
+          <t>6,03; 10,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 14,95</t>
+          <t>10,49; 15,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,02</t>
+          <t>4,6; 9,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 15,98</t>
+          <t>9,64; 16,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 13,62</t>
+          <t>7,63; 13,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 12,68</t>
+          <t>6,94; 12,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,12</t>
+          <t>5,58; 10,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 18,29</t>
+          <t>11,86; 18,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,05</t>
+          <t>10,16; 16,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 14,45</t>
+          <t>10,02; 14,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,85</t>
+          <t>5,71; 8,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 15,99</t>
+          <t>11,52; 15,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,04</t>
+          <t>9,71; 14,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,81</t>
+          <t>9,04; 12,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,19</t>
+          <t>5,17; 11,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 13,93</t>
+          <t>7,38; 14,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 15,79</t>
+          <t>8,69; 15,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,86; 18,75</t>
+          <t>11,7; 18,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,21</t>
+          <t>5,62; 11,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 15,95</t>
+          <t>8,87; 16,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,69</t>
+          <t>9,98; 17,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 18,73</t>
+          <t>12,59; 18,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 10,34</t>
+          <t>6,2; 10,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,03</t>
+          <t>9,2; 14,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 15,47</t>
+          <t>10,17; 15,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 17,73</t>
+          <t>13,41; 17,93</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,99</t>
+          <t>2,75; 7,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,14</t>
+          <t>7,21; 14,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 14,11</t>
+          <t>7,94; 14,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 16,13</t>
+          <t>8,64; 16,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,68</t>
+          <t>3,26; 7,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 17,11</t>
+          <t>10,46; 17,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,15</t>
+          <t>9,96; 17,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 14,05</t>
+          <t>6,63; 14,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,52</t>
+          <t>3,46; 6,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,33</t>
+          <t>9,82; 14,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,4</t>
+          <t>9,58; 14,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 13,74</t>
+          <t>8,14; 13,86</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,57</t>
+          <t>3,83; 11,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 19,0</t>
+          <t>9,61; 19,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 17,22</t>
+          <t>7,79; 16,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 21,02</t>
+          <t>12,89; 21,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,96</t>
+          <t>3,32; 10,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,4; 24,5</t>
+          <t>14,14; 24,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 18,6</t>
+          <t>9,67; 18,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 25,45</t>
+          <t>18,4; 25,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,37</t>
+          <t>4,49; 9,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 20,09</t>
+          <t>13,48; 20,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 16,4</t>
+          <t>9,96; 16,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,3</t>
+          <t>16,95; 22,49</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,92</t>
+          <t>2,81; 8,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,45</t>
+          <t>9,26; 17,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,76</t>
+          <t>5,96; 12,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,4; 25,37</t>
+          <t>17,47; 25,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,08</t>
+          <t>7,76; 15,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,41</t>
+          <t>9,61; 17,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,33</t>
+          <t>6,01; 13,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,53</t>
+          <t>14,06; 20,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,54</t>
+          <t>5,95; 10,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,16</t>
+          <t>10,51; 16,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,68</t>
+          <t>6,66; 11,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,2; 21,51</t>
+          <t>16,56; 21,47</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,03</t>
+          <t>4,02; 7,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 13,3</t>
+          <t>8,38; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,33</t>
+          <t>6,12; 10,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,93</t>
+          <t>8,36; 13,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,06</t>
+          <t>5,68; 10,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,64</t>
+          <t>8,62; 13,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,92</t>
+          <t>5,94; 10,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,59; 63,29</t>
+          <t>13,4; 67,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,21</t>
+          <t>5,26; 8,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,5</t>
+          <t>9,0; 12,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,6</t>
+          <t>6,47; 9,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,87; 53,91</t>
+          <t>11,79; 51,67</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,82</t>
+          <t>4,29; 7,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,13</t>
+          <t>5,32; 9,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,08</t>
+          <t>6,88; 10,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 11,17</t>
+          <t>3,59; 11,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,96</t>
+          <t>6,82; 11,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,63</t>
+          <t>8,13; 12,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,45</t>
+          <t>8,89; 13,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 13,99</t>
+          <t>10,2; 14,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,61</t>
+          <t>5,96; 8,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,13</t>
+          <t>7,29; 10,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 11,53</t>
+          <t>8,33; 11,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,87</t>
+          <t>5,7; 11,74</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,64</t>
+          <t>5,02; 6,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,3</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,5; 10,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,83</t>
+          <t>8,53; 12,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,8</t>
+          <t>6,98; 8,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,16; 13,39</t>
+          <t>11,21; 13,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,91; 12,15</t>
+          <t>9,84; 12,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,43; 34,41</t>
+          <t>13,31; 32,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,52</t>
+          <t>6,32; 7,55</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,07</t>
+          <t>10,5; 12,13</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,44; 10,98</t>
+          <t>9,45; 10,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,29; 24,35</t>
+          <t>12,19; 24,24</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5956; 18123</t>
+          <t>5608; 18388</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17441; 39604</t>
+          <t>17005; 38732</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13032; 30541</t>
+          <t>12796; 30155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28683; 51255</t>
+          <t>28634; 49866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12849; 29812</t>
+          <t>13072; 31129</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18115; 39603</t>
+          <t>18326; 39795</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19404; 39200</t>
+          <t>18735; 39208</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30453; 46368</t>
+          <t>29965; 47220</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21792; 43632</t>
+          <t>21567; 43076</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41026; 72975</t>
+          <t>40989; 72941</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36333; 63491</t>
+          <t>35126; 62356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62937; 89882</t>
+          <t>63080; 90431</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21922; 44494</t>
+          <t>22663; 44507</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47550; 80780</t>
+          <t>48709; 81552</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38981; 68431</t>
+          <t>38345; 66558</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36014; 65609</t>
+          <t>35901; 64451</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28505; 51007</t>
+          <t>28119; 50623</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61389; 95598</t>
+          <t>61989; 96346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52395; 83945</t>
+          <t>53139; 85945</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50224; 74232</t>
+          <t>51465; 75228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56481; 88234</t>
+          <t>56891; 88575</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118176; 164449</t>
+          <t>118428; 164365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98224; 143976</t>
+          <t>99633; 143968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94635; 132036</t>
+          <t>93256; 128918</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17126; 35670</t>
+          <t>16477; 35767</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23395; 45025</t>
+          <t>23848; 45422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28106; 50298</t>
+          <t>27697; 50263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37473; 59259</t>
+          <t>36977; 59298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18811; 40948</t>
+          <t>18843; 38713</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30219; 54395</t>
+          <t>30252; 55435</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31693; 59502</t>
+          <t>33580; 59387</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45265; 65397</t>
+          <t>43954; 65254</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40111; 67641</t>
+          <t>40532; 67319</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59595; 93148</t>
+          <t>61123; 94402</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66834; 101339</t>
+          <t>66575; 99874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87044; 117963</t>
+          <t>89179; 119295</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9721; 25081</t>
+          <t>9863; 25178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27377; 52897</t>
+          <t>26974; 53195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28472; 52218</t>
+          <t>29374; 52961</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27094; 50408</t>
+          <t>27008; 50067</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11783; 28514</t>
+          <t>12116; 28115</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39242; 66396</t>
+          <t>40584; 66084</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38009; 66425</t>
+          <t>38575; 66782</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29855; 66816</t>
+          <t>31533; 68890</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25388; 47596</t>
+          <t>25298; 47279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72457; 109154</t>
+          <t>74833; 112255</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73863; 109041</t>
+          <t>72543; 109847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67327; 108323</t>
+          <t>64129; 109258</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8947; 25554</t>
+          <t>7786; 23391</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19767; 40395</t>
+          <t>20432; 40917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17933; 36373</t>
+          <t>16445; 35280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22396; 37574</t>
+          <t>23047; 38378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6546; 20690</t>
+          <t>6885; 21350</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29425; 53791</t>
+          <t>31050; 54008</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20863; 40653</t>
+          <t>21129; 40873</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38454; 53096</t>
+          <t>38391; 53253</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17561; 38526</t>
+          <t>18442; 38855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55556; 86831</t>
+          <t>58263; 90315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41535; 70486</t>
+          <t>42811; 72521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>64933; 86396</t>
+          <t>65661; 87110</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6808; 21448</t>
+          <t>7621; 22413</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25725; 47801</t>
+          <t>25372; 47840</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15325; 33567</t>
+          <t>15673; 33452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46914; 68414</t>
+          <t>47104; 68449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21623; 41953</t>
+          <t>21587; 42244</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26569; 48597</t>
+          <t>26837; 48656</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17227; 36418</t>
+          <t>16419; 36035</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35946; 52761</t>
+          <t>36138; 52402</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34051; 57851</t>
+          <t>32685; 58780</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55723; 89410</t>
+          <t>58140; 91129</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36038; 62614</t>
+          <t>35711; 62071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85311; 113283</t>
+          <t>87196; 113103</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24990; 49362</t>
+          <t>24720; 46693</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>54048; 88034</t>
+          <t>55475; 88402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37945; 67827</t>
+          <t>40210; 68701</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52834; 80746</t>
+          <t>52203; 81525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37093; 64234</t>
+          <t>36272; 63825</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58935; 94462</t>
+          <t>59728; 94784</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40470; 68572</t>
+          <t>41036; 72671</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>115400; 537503</t>
+          <t>113810; 575411</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67526; 102873</t>
+          <t>65898; 101772</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120458; 169403</t>
+          <t>121876; 171436</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87955; 129341</t>
+          <t>87195; 127701</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>174948; 794325</t>
+          <t>173702; 761311</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31858; 58099</t>
+          <t>31896; 57167</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>40350; 70924</t>
+          <t>41344; 72540</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53290; 86285</t>
+          <t>53601; 85227</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30519; 103742</t>
+          <t>33349; 103480</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52909; 85881</t>
+          <t>53411; 86525</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66905; 103796</t>
+          <t>66806; 102243</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72419; 111119</t>
+          <t>73474; 112586</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>73562; 100021</t>
+          <t>72906; 100757</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>93043; 131480</t>
+          <t>90922; 131439</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>115113; 162003</t>
+          <t>116554; 163524</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>137432; 185004</t>
+          <t>133731; 184748</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>93445; 195072</t>
+          <t>93669; 192930</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>164412; 217366</t>
+          <t>164340; 218178</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>311936; 386535</t>
+          <t>315960; 387073</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>283875; 351976</t>
+          <t>288562; 356536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>310253; 443635</t>
+          <t>294988; 442832</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>238111; 297241</t>
+          <t>235995; 297745</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>395711; 474950</t>
+          <t>397571; 482700</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>351406; 430726</t>
+          <t>348835; 426247</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>491218; 1258568</t>
+          <t>486816; 1202240</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>413344; 500464</t>
+          <t>420869; 502330</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>734156; 840868</t>
+          <t>731552; 845405</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>655378; 761595</t>
+          <t>655952; 761295</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>874918; 1732706</t>
+          <t>867714; 1724811</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A15-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,74</t>
+          <t>2,06; 6,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,22</t>
+          <t>5,46; 12,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,27</t>
+          <t>4,3; 10,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 16,01</t>
+          <t>8,95; 15,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,93</t>
+          <t>5,16; 12,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,15</t>
+          <t>6,6; 14,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 13,58</t>
+          <t>6,73; 14,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 16,3</t>
+          <t>9,96; 15,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,07</t>
+          <t>4,11; 8,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 12,7</t>
+          <t>6,76; 11,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,71</t>
+          <t>6,26; 11,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,04</t>
+          <t>10,31; 14,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,03</t>
+          <t>4,36; 8,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,13</t>
+          <t>9,52; 16,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,24</t>
+          <t>7,8; 13,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,46</t>
+          <t>6,96; 12,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,05</t>
+          <t>5,64; 10,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 18,43</t>
+          <t>12,01; 18,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 16,43</t>
+          <t>10,03; 16,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,64</t>
+          <t>9,65; 14,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,88</t>
+          <t>5,63; 8,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,98</t>
+          <t>11,63; 16,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,04</t>
+          <t>9,8; 13,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,5</t>
+          <t>8,97; 12,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,22</t>
+          <t>5,29; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,06</t>
+          <t>7,43; 14,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,78</t>
+          <t>8,98; 15,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 18,76</t>
+          <t>11,72; 18,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 11,54</t>
+          <t>5,54; 11,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,26</t>
+          <t>8,91; 16,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,66</t>
+          <t>9,9; 17,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 18,69</t>
+          <t>12,69; 18,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,29</t>
+          <t>5,84; 10,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,21</t>
+          <t>9,01; 13,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 15,25</t>
+          <t>10,22; 15,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 17,93</t>
+          <t>12,99; 17,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,02</t>
+          <t>2,57; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 14,22</t>
+          <t>7,25; 14,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,32</t>
+          <t>7,88; 14,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 16,02</t>
+          <t>8,33; 15,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,57</t>
+          <t>3,32; 7,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 17,03</t>
+          <t>10,38; 17,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 17,24</t>
+          <t>9,75; 16,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,48</t>
+          <t>10,7; 15,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,48</t>
+          <t>3,51; 6,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,73</t>
+          <t>9,83; 14,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,51</t>
+          <t>9,64; 14,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,86</t>
+          <t>10,32; 14,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,51</t>
+          <t>4,21; 12,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 19,24</t>
+          <t>9,28; 19,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,7</t>
+          <t>8,28; 16,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,47</t>
+          <t>11,67; 19,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,28</t>
+          <t>3,04; 10,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 24,59</t>
+          <t>13,56; 24,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,7</t>
+          <t>9,39; 18,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,4; 25,52</t>
+          <t>17,98; 24,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,45</t>
+          <t>4,37; 9,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 20,9</t>
+          <t>12,78; 20,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,87</t>
+          <t>10,1; 16,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,49</t>
+          <t>15,62; 20,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,28</t>
+          <t>2,83; 8,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 17,46</t>
+          <t>9,25; 17,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,71</t>
+          <t>5,98; 12,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,47; 25,39</t>
+          <t>16,56; 24,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,19</t>
+          <t>7,85; 15,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,43</t>
+          <t>9,91; 18,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 13,19</t>
+          <t>5,88; 13,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,06; 20,39</t>
+          <t>13,89; 20,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,71</t>
+          <t>6,06; 10,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,48</t>
+          <t>10,44; 16,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,58</t>
+          <t>6,49; 11,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,47</t>
+          <t>16,16; 21,4</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,59</t>
+          <t>4,01; 7,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,35</t>
+          <t>8,3; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,46</t>
+          <t>5,83; 10,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,36; 13,06</t>
+          <t>8,83; 13,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,0</t>
+          <t>5,66; 10,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,68</t>
+          <t>8,49; 13,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,51</t>
+          <t>5,7; 10,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,4; 67,75</t>
+          <t>12,17; 16,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,12</t>
+          <t>5,47; 8,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,65</t>
+          <t>9,07; 12,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,47</t>
+          <t>6,57; 9,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,79; 51,67</t>
+          <t>11,21; 14,33</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,7</t>
+          <t>4,36; 7,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,34</t>
+          <t>5,24; 9,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,95</t>
+          <t>6,99; 11,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,14</t>
+          <t>8,3; 12,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 11,04</t>
+          <t>6,82; 11,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 12,45</t>
+          <t>7,99; 12,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,63</t>
+          <t>8,82; 13,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,09</t>
+          <t>10,18; 13,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,61</t>
+          <t>6,07; 8,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 10,23</t>
+          <t>7,23; 10,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,51</t>
+          <t>8,47; 11,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,74</t>
+          <t>9,81; 12,52</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,66</t>
+          <t>5,02; 6,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,31</t>
+          <t>9,3; 11,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,5</t>
+          <t>8,36; 10,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,8</t>
+          <t>11,04; 12,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,81</t>
+          <t>7,0; 8,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,61</t>
+          <t>11,21; 13,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,03</t>
+          <t>10,02; 12,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,31; 32,87</t>
+          <t>13,03; 14,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,55</t>
+          <t>6,31; 7,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,13</t>
+          <t>10,59; 12,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,97</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,19; 24,24</t>
+          <t>12,28; 13,68</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>78369</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5608; 18388</t>
+          <t>5614; 18030</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17005; 38732</t>
+          <t>16011; 37567</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12796; 30155</t>
+          <t>12640; 31096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28634; 49866</t>
+          <t>28548; 50962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13072; 31129</t>
+          <t>13456; 31488</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18326; 39795</t>
+          <t>18578; 39936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18735; 39208</t>
+          <t>19431; 41146</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29965; 47220</t>
+          <t>31475; 48788</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21567; 43076</t>
+          <t>21929; 43893</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40989; 72941</t>
+          <t>38821; 67460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35126; 62356</t>
+          <t>36466; 65070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63080; 90431</t>
+          <t>65446; 92693</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48798</t>
+          <t>50475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>110988</t>
+          <t>115678</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22663; 44507</t>
+          <t>21513; 43585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48709; 81552</t>
+          <t>48118; 81283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38345; 66558</t>
+          <t>39203; 66042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35901; 64451</t>
+          <t>36880; 65987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28119; 50623</t>
+          <t>28434; 51620</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61989; 96346</t>
+          <t>62805; 96274</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53139; 85945</t>
+          <t>52447; 83681</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51465; 75228</t>
+          <t>52620; 78075</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56891; 88575</t>
+          <t>56138; 88550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118428; 164365</t>
+          <t>119542; 168221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99633; 143968</t>
+          <t>100486; 143131</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93256; 128918</t>
+          <t>96456; 137520</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>55764</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>102258</t>
+          <t>102671</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16477; 35767</t>
+          <t>16867; 34698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23848; 45422</t>
+          <t>24000; 46596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27697; 50263</t>
+          <t>28609; 49730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36977; 59298</t>
+          <t>37046; 59781</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18843; 38713</t>
+          <t>18588; 38451</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30252; 55435</t>
+          <t>30379; 56256</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33580; 59387</t>
+          <t>33303; 59102</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43954; 65254</t>
+          <t>45209; 67109</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40532; 67319</t>
+          <t>38222; 65906</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61123; 94402</t>
+          <t>59832; 91969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66575; 99874</t>
+          <t>66932; 101706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89179; 119295</t>
+          <t>87347; 117816</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>42151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>54806</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>96957</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9863; 25178</t>
+          <t>9220; 24601</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26974; 53195</t>
+          <t>27110; 53722</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29374; 52961</t>
+          <t>29142; 52494</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27008; 50067</t>
+          <t>31101; 56566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12116; 28115</t>
+          <t>12346; 29540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40584; 66084</t>
+          <t>40260; 67248</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38575; 66782</t>
+          <t>37773; 65660</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31533; 68890</t>
+          <t>45149; 65885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25298; 47279</t>
+          <t>25627; 47743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74833; 112255</t>
+          <t>74870; 112587</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72543; 109847</t>
+          <t>72989; 110245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64129; 109258</t>
+          <t>82068; 114340</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75190</t>
+          <t>79230</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7786; 23391</t>
+          <t>8564; 25412</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20432; 40917</t>
+          <t>19731; 40956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16445; 35280</t>
+          <t>17498; 35744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23047; 38378</t>
+          <t>24006; 39829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6885; 21350</t>
+          <t>6317; 20799</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31050; 54008</t>
+          <t>29767; 53414</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21129; 40873</t>
+          <t>20526; 40415</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38391; 53253</t>
+          <t>40860; 55626</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18442; 38855</t>
+          <t>17963; 38636</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58263; 90315</t>
+          <t>55219; 88201</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42811; 72521</t>
+          <t>43404; 70237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65661; 87110</t>
+          <t>67634; 90191</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>100460</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7621; 22413</t>
+          <t>7657; 22739</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25372; 47840</t>
+          <t>25349; 46927</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15673; 33452</t>
+          <t>15745; 34147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47104; 68449</t>
+          <t>44828; 67433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21587; 42244</t>
+          <t>21842; 43324</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26837; 48656</t>
+          <t>27656; 50364</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16419; 36035</t>
+          <t>16066; 36404</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36138; 52402</t>
+          <t>36626; 53536</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32685; 58780</t>
+          <t>33256; 58813</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58140; 91129</t>
+          <t>57731; 90248</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35711; 62071</t>
+          <t>34799; 62146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>87196; 113103</t>
+          <t>86363; 114363</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66470</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>296202</t>
+          <t>110175</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>362672</t>
+          <t>188987</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24720; 46693</t>
+          <t>24655; 47415</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55475; 88402</t>
+          <t>54912; 88345</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40210; 68701</t>
+          <t>38258; 67514</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52203; 81525</t>
+          <t>63522; 98227</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36272; 63825</t>
+          <t>36100; 64623</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59728; 94784</t>
+          <t>58844; 93599</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41036; 72671</t>
+          <t>39396; 69323</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>113810; 575411</t>
+          <t>93985; 128186</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65898; 101772</t>
+          <t>68598; 102685</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121876; 171436</t>
+          <t>122817; 169553</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87195; 127701</t>
+          <t>88604; 128142</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>173702; 761311</t>
+          <t>167275; 213825</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71801</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>86484</t>
+          <t>99758</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>158285</t>
+          <t>179471</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31896; 57167</t>
+          <t>32382; 56393</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>41344; 72540</t>
+          <t>40693; 72009</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53601; 85227</t>
+          <t>54391; 87933</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33349; 103480</t>
+          <t>66230; 97279</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53411; 86525</t>
+          <t>53442; 86650</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66806; 102243</t>
+          <t>65622; 102254</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73474; 112586</t>
+          <t>72835; 111153</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>72906; 100757</t>
+          <t>84535; 115038</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>90922; 131439</t>
+          <t>92603; 132570</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>116554; 163524</t>
+          <t>115645; 159874</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133731; 184748</t>
+          <t>135914; 187692</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>93669; 192930</t>
+          <t>159793; 203894</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>164340; 218178</t>
+          <t>164565; 216536</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>315960; 387073</t>
+          <t>318298; 393069</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>288562; 356536</t>
+          <t>283741; 351265</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>294988; 442832</t>
+          <t>390015; 458262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>235995; 297745</t>
+          <t>236389; 297601</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>397571; 482700</t>
+          <t>397636; 475543</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>348835; 426247</t>
+          <t>355114; 430273</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>486816; 1202240</t>
+          <t>486233; 551151</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>420869; 502330</t>
+          <t>419808; 496259</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>731552; 845405</t>
+          <t>738161; 841006</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>655952; 761295</t>
+          <t>657075; 762250</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>867714; 1724811</t>
+          <t>891729; 993896</t>
         </is>
       </c>
     </row>
